--- a/UTCUTS/B1_Scenario_Config_Main.xlsx
+++ b/UTCUTS/B1_Scenario_Config_Main.xlsx
@@ -27940,5 +27940,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F52C5FE-0F0B-41EB-91B0-E24D09E88B87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8732E339-923D-4173-A759-635500852E53}"/>
 </file>